--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -648,61 +648,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 217792억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 217794억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228096억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 228181억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235419억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235585억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 236111억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 236906억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235071억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235934억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 233004억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 233855억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 229752억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 230591억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 225363억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 225644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 219283억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 219564억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 211566억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 211847억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1179억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1180억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1380억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1381억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1600억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1602억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1788억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1791억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1871억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1874억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2061억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2065억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1755,61 +1755,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 217792억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 217794억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228096억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 228181억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235419억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235585억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 236111억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 236906억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235071억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235934억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 233004억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 233855억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 229752억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 230591억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 225363억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 225644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 219283억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 219564억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 211566억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 211847억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2234,37 +2234,37 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1179억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1180억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1380억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1381억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1600억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1602억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1788억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1791억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1871억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1874억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2061억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2065억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -6491,36 +6491,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.08025</v>
+        <v>0.08026</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.430583</v>
+        <v>0.431119</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.316643</v>
+        <v>0.317577</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.090032</v>
+        <v>0.093697</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.079334</v>
+        <v>0.083288</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.021518</v>
+        <v>0.024864</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.02407</v>
+        <v>-0.021203</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.04552</v>
+        <v>-0.047534</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.067161</v>
+        <v>-0.069384</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.092005</v>
+        <v>-0.094112</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6647,32 +6647,32 @@
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
+        <v>0.06289699999999999</v>
+      </c>
+      <c r="AG22" s="24" t="n">
+        <v>0.062898</v>
+      </c>
+      <c r="AH22" s="24" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="AI22" s="24" t="n">
         <v>0.062901</v>
-      </c>
-      <c r="AG22" s="24" t="n">
-        <v>0.06289699999999999</v>
-      </c>
-      <c r="AH22" s="24" t="n">
-        <v>0.062901</v>
-      </c>
-      <c r="AI22" s="24" t="n">
-        <v>0.0629</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.06289699999999999</v>
+        <v>0.062898</v>
       </c>
       <c r="AL22" s="24" t="n">
+        <v>0.062899</v>
+      </c>
+      <c r="AM22" s="24" t="n">
+        <v>0.062901</v>
+      </c>
+      <c r="AN22" s="24" t="n">
         <v>0.0629</v>
-      </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.062899</v>
-      </c>
-      <c r="AN22" s="24" t="n">
-        <v>0.06289699999999999</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6792,23 +6792,23 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109964</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109964</v>
       </c>
       <c r="AI23" s="24" t="n">
         <v>0.109964</v>
@@ -6818,13 +6818,13 @@
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109965</v>
+        <v>0.109964</v>
       </c>
       <c r="AL23" s="24" t="n">
         <v>0.109962</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109966</v>
+        <v>0.109962</v>
       </c>
       <c r="AN23" s="24" t="n">
         <v>0.109965</v>
@@ -7082,26 +7082,26 @@
         <v>6.08</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>6.57</v>
+        <v>6.58</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>7.69</v>
+        <v>7.7</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>8.92</v>
+        <v>8.93</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>10.43</v>
+        <v>10.45</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>11.5</v>
+        <v>11.52</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7379,20 +7379,20 @@
         <v>0.240422</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.240438</v>
+        <v>0.240415</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.240426</v>
+        <v>0.240422</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.240435</v>
+        <v>0.240439</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.240413</v>
+        <v>0.240419</v>
       </c>
       <c r="AI27" s="24" t="n">
         <v>0.24045</v>
@@ -7402,16 +7402,16 @@
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.24042</v>
+        <v>0.240453</v>
       </c>
       <c r="AL27" s="24" t="n">
-        <v>0.240435</v>
+        <v>0.240428</v>
       </c>
       <c r="AM27" s="24" t="n">
-        <v>0.240437</v>
+        <v>0.240449</v>
       </c>
       <c r="AN27" s="24" t="n">
-        <v>0.240417</v>
+        <v>0.24043</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7812,17 +7812,17 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="AL30" s="29" t="n">
         <v>119.77</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN30" s="29" t="n">
         <v>0</v>
@@ -7940,17 +7940,17 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="AL31" s="29" t="n">
         <v>119.77</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN31" s="29" t="n">
         <v>0</v>
@@ -8163,33 +8163,33 @@
         <v>0.366012</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.310132</v>
+        <v>0.310249</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.211441</v>
+        <v>0.211578</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.082709</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.170676</v>
+        <v>0.171157</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.159651</v>
+        <v>0.160036</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.117865</v>
+        <v>0.118107</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.046439</v>
+        <v>0.046504</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.102006</v>
+        <v>0.101957</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.09862899999999999</v>
+        <v>0.098593</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8291,33 +8291,33 @@
         <v>0.364471</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.309152</v>
+        <v>0.309268</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.210952</v>
+        <v>0.211077</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.08193</v>
+        <v>0.082547</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.170368</v>
+        <v>0.170857</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.159404</v>
+        <v>0.159781</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.117708</v>
+        <v>0.117956</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.046384</v>
+        <v>0.046443</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.10189</v>
+        <v>0.101841</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.09853199999999999</v>
+        <v>0.098491</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8959,23 +8959,23 @@
         <v>-0.329532</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.046358</v>
+        <v>-0.048013</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.017825</v>
+        <v>0.01426</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.041894</v>
+        <v>0.038251</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.020408</v>
+        <v>-0.02381</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>0.012153</v>
+        <v>0.012174</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.043783</v>
+        <v>0.045694</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9366,23 +9366,23 @@
         <v/>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.109963</v>
+        <v>0.109962</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109964</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109964</v>
       </c>
       <c r="AI43" s="24" t="n">
         <v>0.109964</v>
@@ -9392,13 +9392,13 @@
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.109965</v>
+        <v>0.109964</v>
       </c>
       <c r="AL43" s="24" t="n">
         <v>0.109962</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.109966</v>
+        <v>0.109962</v>
       </c>
       <c r="AN43" s="24" t="n">
         <v>0.109965</v>
@@ -39461,7 +39461,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2655</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="30">
@@ -39501,7 +39501,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2736</v>
+        <v>0.2739</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228181억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 229097억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235585억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239930억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 236906억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 248440억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235934억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 259314억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 233855억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 273365억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 230591억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 289162억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 225644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 304889억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 219564억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 319806억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 211847억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 332140억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -900,49 +900,49 @@
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 900억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 901억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1090억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1094억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1180억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1194억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1381억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1415억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1602억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1672억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1791억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1908억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1874억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2060억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2065억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2335억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1761,55 +1761,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228181억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 229097억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235585억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239930억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 236906억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248440억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235934억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 259314억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 233855억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 273365억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 230591억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 289162억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 225644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 304889억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 219564억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 319806억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 211847억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 332140억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -2222,49 +2222,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 900억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 901억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1090억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1094억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1180억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1194억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1381억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1415억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1602억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1672억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1791억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1908억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1874억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2060억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2065억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2335억 × 2.23% − 총차입금 0억 × 8.76% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4315,7 +4315,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 15.6, "op_wape_pct": 35.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 1580.22, "rev_act": 2011.06, "op_pred": 139.89, "op_act": 235.1}, {"q": "2025Q4", "rev_pred": 2063.1, "rev_act": 1753.91, "op_pred": 182.64, "op_act": 195.83}, {"q": "2026Q1", "rev_pred": 1731.59, "rev_act": 1691.29, "op_pred": 153.29, "op_act": 198.54}, {"q": "2026Q2", "rev_pred": 1825.43, "rev_act": 2245.34, "op_pred": 161.6, "op_act": 359.4}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 15.6, "op_wape_pct": 35.5, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": 11.4, "wape_trend": 13.8, "adopted": true}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1580.22, "rev_act": 2011.06, "op_pred": 139.89, "op_act": 235.1}, {"q": "2025Q4", "rev_pred": 2063.1, "rev_act": 1753.91, "op_pred": 182.64, "op_act": 195.83}, {"q": "2026Q1", "rev_pred": 1731.59, "rev_act": 1691.29, "op_pred": 153.29, "op_act": 198.54}, {"q": "2026Q2", "rev_pred": 1825.43, "rev_act": 2245.34, "op_pred": 161.6, "op_act": 359.4}]}</t>
         </is>
       </c>
     </row>
@@ -6494,33 +6494,33 @@
         <v>0.08026</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.431119</v>
+        <v>0.436861</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.317577</v>
+        <v>0.341878</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.093697</v>
+        <v>0.14695</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.083288</v>
+        <v>0.190636</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.024864</v>
+        <v>0.193232</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.021203</v>
+        <v>0.20519</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.047534</v>
+        <v>0.227213</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.069384</v>
+        <v>0.233277</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.094112</v>
+        <v>0.215004</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6640,39 +6640,39 @@
         <v>0.062901</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.062899</v>
+        <v>0.062898</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.06289699999999999</v>
+        <v>0.062899</v>
       </c>
       <c r="AG22" s="24" t="n">
         <v>0.062898</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.0629</v>
+        <v>0.062901</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.062901</v>
+        <v>0.062898</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.062898</v>
+        <v>0.062899</v>
       </c>
       <c r="AL22" s="24" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="AM22" s="24" t="n">
         <v>0.062899</v>
       </c>
-      <c r="AM22" s="24" t="n">
-        <v>0.062901</v>
-      </c>
       <c r="AN22" s="24" t="n">
-        <v>0.0629</v>
+        <v>0.062899</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -6795,7 +6795,7 @@
         <v>0.109962</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109963</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
@@ -6808,26 +6808,26 @@
         <v>0.109964</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109964</v>
+        <v>0.109962</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109964</v>
+        <v>0.109963</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
+        <v>0.109963</v>
+      </c>
+      <c r="AL23" s="24" t="n">
+        <v>0.109963</v>
+      </c>
+      <c r="AM23" s="24" t="n">
+        <v>0.109965</v>
+      </c>
+      <c r="AN23" s="24" t="n">
         <v>0.109964</v>
-      </c>
-      <c r="AL23" s="24" t="n">
-        <v>0.109962</v>
-      </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.109962</v>
-      </c>
-      <c r="AN23" s="24" t="n">
-        <v>0.109965</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7079,29 +7079,29 @@
         <v>5.02</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>6.58</v>
+        <v>6.66</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>7.7</v>
+        <v>7.89</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>8.93</v>
+        <v>9.33</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>9.99</v>
+        <v>10.64</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>10.45</v>
+        <v>11.49</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>11.52</v>
+        <v>13.02</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -7379,39 +7379,39 @@
         <v>0.240422</v>
       </c>
       <c r="AD27" s="24" t="n">
-        <v>0.240415</v>
+        <v>0.240434</v>
       </c>
       <c r="AE27" s="25">
         <f>IFERROR(subQ!AE14/subQ!AE13,"")</f>
         <v/>
       </c>
       <c r="AF27" s="24" t="n">
-        <v>0.240422</v>
+        <v>0.240426</v>
       </c>
       <c r="AG27" s="24" t="n">
-        <v>0.240439</v>
+        <v>0.240416</v>
       </c>
       <c r="AH27" s="24" t="n">
-        <v>0.240419</v>
+        <v>0.240441</v>
       </c>
       <c r="AI27" s="24" t="n">
-        <v>0.24045</v>
+        <v>0.24043</v>
       </c>
       <c r="AJ27" s="25">
         <f>IFERROR(subQ!AJ14/subQ!AJ13,"")</f>
         <v/>
       </c>
       <c r="AK27" s="24" t="n">
-        <v>0.240453</v>
+        <v>0.240439</v>
       </c>
       <c r="AL27" s="24" t="n">
+        <v>0.240444</v>
+      </c>
+      <c r="AM27" s="24" t="n">
         <v>0.240428</v>
       </c>
-      <c r="AM27" s="24" t="n">
-        <v>0.240449</v>
-      </c>
       <c r="AN27" s="24" t="n">
-        <v>0.24043</v>
+        <v>0.240435</v>
       </c>
       <c r="AO27" s="25">
         <f>IFERROR(subQ!AO14/subQ!AO13,"")</f>
@@ -7799,7 +7799,7 @@
         <v>0.0037</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
@@ -7809,17 +7809,17 @@
         <v>119.76</v>
       </c>
       <c r="AH30" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI30" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AI30" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>119.77</v>
+        <v>119.76</v>
       </c>
       <c r="AM30" s="29" t="n">
         <v>0</v>
@@ -7927,7 +7927,7 @@
         <v>0.0037</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
@@ -7937,17 +7937,17 @@
         <v>119.76</v>
       </c>
       <c r="AH31" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AI31" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>119.77</v>
+        <v>119.76</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -8163,33 +8163,33 @@
         <v>0.366012</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.310249</v>
+        <v>0.311475</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.211578</v>
+        <v>0.215197</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.082709</v>
+        <v>0.091553</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.171157</v>
+        <v>0.185501</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.160036</v>
+        <v>0.182002</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.118107</v>
+        <v>0.141021</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.046504</v>
+        <v>0.079912</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.101957</v>
+        <v>0.133707</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.098593</v>
+        <v>0.135035</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8291,33 +8291,33 @@
         <v>0.364471</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.309268</v>
+        <v>0.31049</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.211077</v>
+        <v>0.2147</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.082547</v>
+        <v>0.091374</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.170857</v>
+        <v>0.185168</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.159781</v>
+        <v>0.181719</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.117956</v>
+        <v>0.140847</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.046443</v>
+        <v>0.07982300000000001</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.101841</v>
+        <v>0.133569</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.098491</v>
+        <v>0.134911</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -8953,29 +8953,29 @@
       </c>
       <c r="AE40" s="25" t="n"/>
       <c r="AF40" s="24" t="n">
-        <v>-0.571094</v>
+        <v>-0.573438</v>
       </c>
       <c r="AG40" s="24" t="n">
-        <v>-0.329532</v>
+        <v>-0.342075</v>
       </c>
       <c r="AH40" s="24" t="n">
-        <v>-0.048013</v>
+        <v>-0.086093</v>
       </c>
       <c r="AI40" s="24" t="n">
-        <v>0.01426</v>
+        <v>-0.06417100000000001</v>
       </c>
       <c r="AJ40" s="25" t="n"/>
       <c r="AK40" s="24" t="n">
-        <v>0.038251</v>
+        <v>-0.08241800000000001</v>
       </c>
       <c r="AL40" s="24" t="n">
-        <v>-0.02381</v>
+        <v>-0.17851</v>
       </c>
       <c r="AM40" s="24" t="n">
-        <v>0.012174</v>
+        <v>-0.184783</v>
       </c>
       <c r="AN40" s="24" t="n">
-        <v>0.045694</v>
+        <v>-0.188571</v>
       </c>
       <c r="AO40" s="25" t="n"/>
     </row>
@@ -9075,26 +9075,26 @@
         <v>-0.567742</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.454167</v>
+        <v>-0.458333</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.178808</v>
+        <v>-0.18543</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.176056</v>
+        <v>-0.190141</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.164179</v>
+        <v>-0.186567</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>-0.167939</v>
+        <v>-0.192308</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>-0.153226</v>
+        <v>-0.195122</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>-0.145299</v>
+        <v>-0.191304</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -9369,7 +9369,7 @@
         <v>0.109962</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.109962</v>
+        <v>0.109963</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE33,"")</f>
@@ -9382,26 +9382,26 @@
         <v>0.109964</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.109964</v>
+        <v>0.109962</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.109964</v>
+        <v>0.109963</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ33,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
+        <v>0.109963</v>
+      </c>
+      <c r="AL43" s="24" t="n">
+        <v>0.109963</v>
+      </c>
+      <c r="AM43" s="24" t="n">
+        <v>0.109965</v>
+      </c>
+      <c r="AN43" s="24" t="n">
         <v>0.109964</v>
-      </c>
-      <c r="AL43" s="24" t="n">
-        <v>0.109962</v>
-      </c>
-      <c r="AM43" s="24" t="n">
-        <v>0.109962</v>
-      </c>
-      <c r="AN43" s="24" t="n">
-        <v>0.109965</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO33,"")</f>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39461,7 +39461,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2658</v>
+        <v>2705.6</v>
       </c>
     </row>
     <row r="30">
@@ -39481,7 +39481,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.88</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="32">
@@ -39501,7 +39501,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2739</v>
+        <v>0.2788</v>
       </c>
     </row>
     <row r="34">
@@ -39511,7 +39511,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="35">
@@ -39521,7 +39521,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226719억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235943억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235902억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 242825억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 242763억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252822억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 252740억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266843억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266758억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282625억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 282544억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298357억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 298280억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 313279억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 313206억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 325628억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 325560억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226719억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235943억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235902억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 242825억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 242763억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252822억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252740억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266843억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266758억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282625억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 282544억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298357억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298280억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 313279억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 313206억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 325628억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 325560억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16380</v>
+        <v>16170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5774,7 +5774,7 @@
         <v>18760</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>16440</v>
+        <v>16490</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16205</v>
+        <v>16193.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.07645558600000001</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.421945432</v>
+        <v>0.4218257</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319569825</v>
+        <v>0.319345145</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.12102944</v>
+        <v>0.120739951</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.164932881</v>
+        <v>0.164549478</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.176978873</v>
+        <v>0.176705056</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.197860004</v>
+        <v>0.197718921</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.228688684</v>
+        <v>0.228688147</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.239128107</v>
+        <v>0.239246501</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.220297409</v>
+        <v>0.220431976</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.109962953</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109965236</v>
+        <v>0.109962466</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109961555</v>
+        <v>0.109962355</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109964284</v>
+        <v>0.109964871</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109962052</v>
+        <v>0.109962555</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109963037</v>
+        <v>0.109963809</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109962744</v>
+        <v>0.109964491</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109964691</v>
+        <v>0.109964035</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109964415</v>
+        <v>0.109964503</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109963707</v>
+        <v>0.109964091</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.000713559</v>
+        <v>-0.000351389</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>0.008947706999999999</v>
+        <v>-0.00336777</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.003604192</v>
+        <v>0.006512373</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>119.762467731</v>
+        <v>119.76980582</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.0009500240000000001</v>
+        <v>-0.007026614</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.005945381</v>
+        <v>0.010228671</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.00885298</v>
+        <v>0.000496372</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>119.768764634</v>
+        <v>119.770451819</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.00557446</v>
+        <v>0.004694111</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.001783712</v>
+        <v>0.000823607</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.000713559</v>
+        <v>-0.000351389</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.008947706999999999</v>
+        <v>-0.00336777</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.003604192</v>
+        <v>0.006512373</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.762467731</v>
+        <v>119.76980582</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.0009500240000000001</v>
+        <v>-0.007026614</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.005945381</v>
+        <v>0.010228671</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.00885298</v>
+        <v>0.000496372</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.768764634</v>
+        <v>119.770451819</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.00557446</v>
+        <v>0.004694111</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.001783712</v>
+        <v>0.000823607</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>0.363938411</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>0.307943051</v>
+        <v>0.307913816</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>0.21177036</v>
+        <v>0.211741565</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.08687792799999999</v>
+        <v>0.08683581899999999</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>0.182175345</v>
+        <v>0.182131401</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>0.179425339</v>
+        <v>0.179389806</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>0.139330793</v>
+        <v>0.139309388</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.077448613</v>
+        <v>0.07742979899999999</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>0.132836243</v>
+        <v>0.132831521</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>0.134371403</v>
+        <v>0.134366642</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.362406583</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.306968204</v>
+        <v>0.306939061</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.211267449</v>
+        <v>0.211238711</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.086707597</v>
+        <v>0.086665562</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.181855143</v>
+        <v>0.18180278</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.179142986</v>
+        <v>0.179115925</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.139150413</v>
+        <v>0.139135087</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.077360595</v>
+        <v>0.077336037</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.13270107</v>
+        <v>0.132691374</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134245677</v>
+        <v>0.134245856</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>16380</v>
+        <v>16170</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.2404296588482665</v>
+        <v>0.2404292296104523</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06289880561331017</v>
+        <v>0.06289916814967453</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01808517435197157</v>
+        <v>0.01808788223698557</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39450,7 +39450,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2660.8</v>
+        <v>2660.5</v>
       </c>
     </row>
     <row r="30">
@@ -39470,7 +39470,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="32">
@@ -39480,7 +39480,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="33">
@@ -39490,7 +39490,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2742</v>
+        <v>0.2741</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 226684억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235902억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235859억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 242763억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 242694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252740억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 252646억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266758억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266656억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282544억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 282446억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298280억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 298187억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 313206억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 313118억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 325560억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 325479억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226700억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226684억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235902억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235859억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 242763억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 242694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252740억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252646억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266758억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266656억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282544억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 282446억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298280억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 298187억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 313206억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 313118억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 325560억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 325479억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1908,7 +1908,7 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1181억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1180억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1932,13 +1932,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2019억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2018억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2287억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2286억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1968,7 +1968,7 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1181억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1180억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -1992,13 +1992,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2019억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2018억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2287억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2286억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>16170</v>
+        <v>15710</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5774,7 +5774,7 @@
         <v>18760</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>16490</v>
+        <v>16670</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16193.3</v>
+        <v>16087.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.07645558600000001</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.4218257</v>
+        <v>0.421728773</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.319345145</v>
+        <v>0.31910864</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.120739951</v>
+        <v>0.12042374</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.164549478</v>
+        <v>0.164119881</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.176705056</v>
+        <v>0.176336126</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.197718921</v>
+        <v>0.197516809</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.228688147</v>
+        <v>0.228649338</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.239246501</v>
+        <v>0.239354631</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.220431976</v>
+        <v>0.220591143</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.109962953</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109962466</v>
+        <v>0.109961942</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109962355</v>
+        <v>0.109964142</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109964871</v>
+        <v>0.109964106</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109962555</v>
+        <v>0.109963454</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109963809</v>
+        <v>0.109961477</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109964491</v>
+        <v>0.109961597</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109964035</v>
+        <v>0.109962956</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109964503</v>
+        <v>0.109963468</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109964091</v>
+        <v>0.109963803</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-0.000351389</v>
+        <v>-5.3271e-05</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>-0.00336777</v>
+        <v>0.001845643</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>0.006512373</v>
+        <v>0.006623925</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>119.76980582</v>
+        <v>119.759506904</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>-0.007026614</v>
+        <v>0.00733181</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.010228671</v>
+        <v>0.001685015</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.000496372</v>
+        <v>-0.003053277</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>119.770451819</v>
+        <v>119.766760142</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>0.004694111</v>
+        <v>-0.001592881</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.000823607</v>
+        <v>0.004420627</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-0.000351389</v>
+        <v>-5.3271e-05</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.00336777</v>
+        <v>0.001845643</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.006512373</v>
+        <v>0.006623925</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.76980582</v>
+        <v>119.759506904</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.007026614</v>
+        <v>0.00733181</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.010228671</v>
+        <v>0.001685015</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.000496372</v>
+        <v>-0.003053277</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.770451819</v>
+        <v>119.766760142</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.004694111</v>
+        <v>-0.001592881</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.000823607</v>
+        <v>0.004420627</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>0.363938411</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>0.307913816</v>
+        <v>0.307884582</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>0.211741565</v>
+        <v>0.211712769</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.08683581899999999</v>
+        <v>0.086784482</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>0.182131401</v>
+        <v>0.182080508</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>0.179389806</v>
+        <v>0.17934966</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>0.139309388</v>
+        <v>0.139284431</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.07742979899999999</v>
+        <v>0.077396601</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>0.132831521</v>
+        <v>0.132826449</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>0.134366642</v>
+        <v>0.134366586</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.362406583</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.306939061</v>
+        <v>0.306924489</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.211238711</v>
+        <v>0.211196468</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.086665562</v>
+        <v>0.086614318</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.18180278</v>
+        <v>0.18176042</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.179115925</v>
+        <v>0.17906735</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.139135087</v>
+        <v>0.139110133</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.077336037</v>
+        <v>0.077308197</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132691374</v>
+        <v>0.132680665</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134245856</v>
+        <v>0.134241398</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>16170</v>
+        <v>15710</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,130원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,370원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.2404292296104523</v>
+        <v>0.240429209745279</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06289916814967453</v>
+        <v>0.06289920193465065</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01808788223698557</v>
+        <v>0.01809094904430341</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39450,7 +39450,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2660.5</v>
+        <v>2660.1</v>
       </c>
     </row>
     <row r="30">
@@ -39470,7 +39470,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.08</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="32">
@@ -39480,7 +39480,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -657,61 +657,61 @@
     <comment ref="AC21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 217027억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 216969억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226684억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 226522억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235859억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235690억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 242694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 242655억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252646억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 252970억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266656억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267594억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 282446억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 284125억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 298187억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 300696억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 313118억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 316503억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 325479억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 329743억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1524,61 +1524,61 @@
   <commentList>
     <comment ref="AC5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 217027억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 216969억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226684억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226522억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235859억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235690억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 242694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 242655억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252646억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252970억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266656억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267594억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 282446억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 284125억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 298187억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 300696억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 313118억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316503억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 325479억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 329743억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1920,25 +1920,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1645억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1646억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1874억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1876억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2018억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2286억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 2293억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1980,25 +1980,25 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1645억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1646억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1874억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1876억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2018억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2286억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2293억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3844,7 +3844,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -6108,36 +6108,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.07645558600000001</v>
+        <v>0.076167181</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.421728773</v>
+        <v>0.4207139</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.31910864</v>
+        <v>0.318162618</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.12042374</v>
+        <v>0.12024114</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.164119881</v>
+        <v>0.165924297</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.176336126</v>
+        <v>0.181317998</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.197516809</v>
+        <v>0.205503723</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.228649338</v>
+        <v>0.239190242</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.239354631</v>
+        <v>0.251147289</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.220591143</v>
+        <v>0.232248048</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6419,42 +6419,42 @@
         <v/>
       </c>
       <c r="AC23" s="24" t="n">
-        <v>0.109962953</v>
+        <v>0.109964699</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109961942</v>
+        <v>0.109964243</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109964142</v>
+        <v>0.109962322</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109964106</v>
+        <v>0.109962152</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109963454</v>
+        <v>0.109965363</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109961477</v>
+        <v>0.109963243</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109961597</v>
+        <v>0.109962605</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109962956</v>
+        <v>0.109962913</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109963468</v>
+        <v>0.109962719</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109963803</v>
+        <v>0.109964243</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>-5.3271e-05</v>
+        <v>0.003054456</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>0.001845643</v>
+        <v>0.005791502</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>0.006623925</v>
+        <v>-0.002312138</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>119.759506904</v>
+        <v>119.758639774</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.00733181</v>
+        <v>0.007738895</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>0.001685015</v>
+        <v>-0.004856031</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>-0.003053277</v>
+        <v>0.006748675</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>119.766760142</v>
+        <v>119.7639039</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.001592881</v>
+        <v>-0.001411143</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>0.004420627</v>
+        <v>-0.004624914</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>-5.3271e-05</v>
+        <v>0.003054456</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.001845643</v>
+        <v>0.005791502</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.006623925</v>
+        <v>-0.002312138</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.759506904</v>
+        <v>119.758639774</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.00733181</v>
+        <v>0.007738895</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.001685015</v>
+        <v>-0.004856031</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.003053277</v>
+        <v>0.006748675</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.766760142</v>
+        <v>119.7639039</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001592881</v>
+        <v>-0.001411143</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.004420627</v>
+        <v>-0.004624914</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7553,36 +7553,36 @@
         <v/>
       </c>
       <c r="AC31" s="24" t="n">
-        <v>0.363938411</v>
+        <v>0.363838725</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>0.307884582</v>
+        <v>0.307702428</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>0.211712769</v>
+        <v>0.211601234</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.086784482</v>
+        <v>0.086774</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>0.182080508</v>
+        <v>0.182375414</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>0.17934966</v>
+        <v>0.179971566</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>0.139284431</v>
+        <v>0.140035415</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.077396601</v>
+        <v>0.078473445</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>0.132826449</v>
+        <v>0.133945717</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>0.134366586</v>
+        <v>0.135669268</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7681,36 +7681,36 @@
         <v/>
       </c>
       <c r="AC32" s="24" t="n">
-        <v>0.362406583</v>
+        <v>0.36230732</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.306924489</v>
+        <v>0.306728261</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.211196468</v>
+        <v>0.211098596</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.086614318</v>
+        <v>0.086613013</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.18176042</v>
+        <v>0.182036202</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.17906735</v>
+        <v>0.179703911</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.139110133</v>
+        <v>0.139847221</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.077308197</v>
+        <v>0.07838433</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132680665</v>
+        <v>0.133804662</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134241398</v>
+        <v>0.135543259</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.240429209745279</v>
+        <v>0.2404338059623974</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06289920193465065</v>
+        <v>0.06289894808457572</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01809094904430341</v>
+        <v>0.01808871341619431</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39450,7 +39450,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2660.1</v>
+        <v>2658.8</v>
       </c>
     </row>
     <row r="30">
@@ -39490,7 +39490,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2741</v>
+        <v>0.274</v>
       </c>
     </row>
     <row r="34">
@@ -39500,7 +39500,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="35">
@@ -39510,7 +39510,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>29600</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226522억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 226513억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235690억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 235680억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 242655억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 242644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 252970억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 252959억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 267594억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 267593억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 284125억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 284124억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 300696억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 300694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 316503억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 316501억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 329743억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 329741억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1530,55 +1530,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226522억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226513억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235690억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235680억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 242655억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 242644억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 252970억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 252959억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 267594억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 267593억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 284125억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 284124억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 300696억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 300694억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 316503억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 316501억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 329743억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 329741억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1920,7 +1920,7 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1646억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 0분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 1645억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1980,7 +1980,7 @@
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1646억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1645억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4715,35 +4715,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -4834,35 +4834,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -4953,35 +4953,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5072,35 +5072,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5191,35 +5191,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5310,35 +5310,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5429,35 +5429,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5548,35 +5548,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5683,7 +5683,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>15710</v>
+        <v>15210</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -5865,7 +5865,7 @@
         <v>14050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15610</v>
+        <v>15040</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -5956,7 +5956,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>16087.5</v>
+        <v>15904</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6111,33 +6111,33 @@
         <v>0.076167181</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.4207139</v>
+        <v>0.420651184</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.318162618</v>
+        <v>0.318103492</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.12024114</v>
+        <v>0.120192149</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.165924297</v>
+        <v>0.165878091</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.181317998</v>
+        <v>0.181362122</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.205503723</v>
+        <v>0.205548827</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.239190242</v>
+        <v>0.239240461</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.251147289</v>
+        <v>0.251188948</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.232248048</v>
+        <v>0.232249626</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6422,39 +6422,39 @@
         <v>0.109964699</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109964243</v>
+        <v>0.109965084</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109962322</v>
+        <v>0.109962769</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109962152</v>
+        <v>0.109962985</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109965363</v>
+        <v>0.109961795</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109963243</v>
+        <v>0.10996399</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109962605</v>
+        <v>0.109963424</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109962913</v>
+        <v>0.109963265</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109962719</v>
+        <v>0.109963415</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109964243</v>
+        <v>0.109962092</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7169,36 +7169,36 @@
         <v/>
       </c>
       <c r="AC28" s="30" t="n">
-        <v>0.003054456</v>
+        <v>0.004302859</v>
       </c>
       <c r="AD28" s="30" t="n">
-        <v>0.005791502</v>
+        <v>-0.000357605</v>
       </c>
       <c r="AE28" s="31" t="n"/>
       <c r="AF28" s="30" t="n">
-        <v>-0.002312138</v>
+        <v>0.001377941</v>
       </c>
       <c r="AG28" s="30" t="n">
-        <v>119.758639774</v>
+        <v>119.77247058</v>
       </c>
       <c r="AH28" s="30" t="n">
-        <v>0.007738895</v>
+        <v>-0.006046453</v>
       </c>
       <c r="AI28" s="30" t="n">
-        <v>-0.004856031</v>
+        <v>0.006802362</v>
       </c>
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="30" t="n">
-        <v>0.006748675</v>
+        <v>-0.001745432</v>
       </c>
       <c r="AL28" s="30" t="n">
-        <v>119.7639039</v>
+        <v>119.775665751</v>
       </c>
       <c r="AM28" s="30" t="n">
-        <v>-0.001411143</v>
+        <v>0.000386686</v>
       </c>
       <c r="AN28" s="30" t="n">
-        <v>-0.004624914</v>
+        <v>-0.000136652</v>
       </c>
       <c r="AO28" s="31" t="n"/>
     </row>
@@ -7297,36 +7297,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.003054456</v>
+        <v>0.004302859</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.005791502</v>
+        <v>-0.000357605</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002312138</v>
+        <v>0.001377941</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.758639774</v>
+        <v>119.77247058</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.007738895</v>
+        <v>-0.006046453</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.004856031</v>
+        <v>0.006802362</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.006748675</v>
+        <v>-0.001745432</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.7639039</v>
+        <v>119.775665751</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001411143</v>
+        <v>0.000386686</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.004624914</v>
+        <v>-0.000136652</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7556,33 +7556,33 @@
         <v>0.363838725</v>
       </c>
       <c r="AD31" s="24" t="n">
-        <v>0.307702428</v>
+        <v>0.30768781</v>
       </c>
       <c r="AE31" s="25" t="n"/>
       <c r="AF31" s="24" t="n">
-        <v>0.211601234</v>
+        <v>0.211592421</v>
       </c>
       <c r="AG31" s="24" t="n">
-        <v>0.086774</v>
+        <v>0.08677560099999999</v>
       </c>
       <c r="AH31" s="24" t="n">
-        <v>0.182375414</v>
+        <v>0.182361531</v>
       </c>
       <c r="AI31" s="24" t="n">
-        <v>0.179971566</v>
+        <v>0.179976736</v>
       </c>
       <c r="AJ31" s="25" t="n"/>
       <c r="AK31" s="24" t="n">
-        <v>0.140035415</v>
+        <v>0.140038824</v>
       </c>
       <c r="AL31" s="24" t="n">
-        <v>0.078473445</v>
+        <v>0.07847512099999999</v>
       </c>
       <c r="AM31" s="24" t="n">
-        <v>0.133945717</v>
+        <v>0.133948369</v>
       </c>
       <c r="AN31" s="24" t="n">
-        <v>0.135669268</v>
+        <v>0.135671637</v>
       </c>
       <c r="AO31" s="25" t="n"/>
     </row>
@@ -7684,33 +7684,33 @@
         <v>0.36230732</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.306728261</v>
+        <v>0.306713688</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.211098596</v>
+        <v>0.211089798</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.086613013</v>
+        <v>0.0866054</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182036202</v>
+        <v>0.18204083</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.179703911</v>
+        <v>0.179700607</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.139847221</v>
+        <v>0.13985062</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07838433</v>
+        <v>0.078386001</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.133804662</v>
+        <v>0.133807308</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.135543259</v>
+        <v>0.135545623</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8373,11 +8373,11 @@
         </is>
       </c>
       <c r="D40" s="34" t="n">
-        <v>15710</v>
+        <v>15210</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,370원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,130원)</t>
         </is>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D41" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="D47" s="36" t="n">
-        <v>0.2404338059623974</v>
+        <v>0.2404287504301138</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.06289894808457572</v>
+        <v>0.06289902378599706</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="D50" s="36" t="n">
-        <v>0.01808871341619431</v>
+        <v>0.0180890659583183</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39470,7 +39470,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.91</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="32">
@@ -39480,7 +39480,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228868억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 228865억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238683억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 238707억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245612억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 245662억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254586억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254661억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266854억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266956억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281732억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 281830억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297331억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 297424억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 312837억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 312926억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326415억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326497억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228868억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 228865억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238683억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238707억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245612억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245662억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254586억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254661억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266854억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266956억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281732억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 281830억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297331억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297424억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 312837억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 312926억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326415억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326497억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>15210</v>
+        <v>15190</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15904</v>
+        <v>15900</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.435423858</v>
+        <v>0.435406753</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.334901285</v>
+        <v>0.335031363</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.133896099</v>
+        <v>0.134123237</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.168954438</v>
+        <v>0.169299675</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165974873</v>
+        <v>0.166433639</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180359745</v>
+        <v>0.18065219</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210567247</v>
+        <v>0.210705716</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.228808487</v>
+        <v>0.228792108</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.223197648</v>
+        <v>0.223037605</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109961432</v>
+        <v>0.109962742</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109960978</v>
+        <v>0.109963551</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109961587</v>
+        <v>0.109963126</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109964323</v>
+        <v>0.109963349</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109961948</v>
+        <v>0.109964278</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109962438</v>
+        <v>0.109962001</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109964699</v>
+        <v>0.109962537</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109962795</v>
+        <v>0.10996383</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109963071</v>
+        <v>0.109963359</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.006751231</v>
+        <v>0.007168551</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>-0.003553962</v>
+        <v>0.006882867</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.007146049</v>
+        <v>0.00016423</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.762353199</v>
+        <v>119.768259817</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.003718618</v>
+        <v>0.004908224</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>-0.003579036</v>
+        <v>0.005815871</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.006738187</v>
+        <v>-0.006537124</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.768274738</v>
+        <v>119.775295367</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.002603932</v>
+        <v>-0.005363792</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.004674889</v>
+        <v>0.01221158</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.006751231</v>
+        <v>0.007168551</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>-0.003553962</v>
+        <v>0.006882867</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.007146049</v>
+        <v>0.00016423</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.762353199</v>
+        <v>119.768259817</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.003718618</v>
+        <v>0.004908224</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>-0.003579036</v>
+        <v>0.005815871</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.006738187</v>
+        <v>-0.006537124</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.768274738</v>
+        <v>119.775295367</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.002603932</v>
+        <v>-0.005363792</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.004674889</v>
+        <v>0.01221158</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7900,29 +7900,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213351325</v>
+        <v>0.213362478</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08849264699999999</v>
+        <v>0.088528598</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182237309</v>
+        <v>0.182297164</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178308692</v>
+        <v>0.178356413</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.138148204</v>
+        <v>0.138172209</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076563382</v>
+        <v>0.076599483</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132204094</v>
+        <v>0.132213869</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134323141</v>
+        <v>0.134331683</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8024,33 +8024,33 @@
         <v>0.362962457</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.309217234</v>
+        <v>0.309202668</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.212832237</v>
+        <v>0.212867982</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.08831974200000001</v>
+        <v>0.088354814</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.181918561</v>
+        <v>0.181959932</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.17803657</v>
+        <v>0.178085513</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.137963182</v>
+        <v>0.137994068</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.07648194699999999</v>
+        <v>0.076512702</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.132059341</v>
+        <v>0.132074726</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.134202611</v>
+        <v>0.134206805</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8713,11 +8713,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>15210</v>
+        <v>15190</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 16,130원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,660원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404347755341133</v>
+        <v>0.2404320736607506</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.06289940390442782</v>
+        <v>0.06289894853106015</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808579597147935</v>
+        <v>0.01808335959910731</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2680.1</v>
+        <v>2680.3</v>
       </c>
     </row>
     <row r="30">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.68</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228865억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 228862억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238707억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 238693억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245662억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 245637억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254661억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254626억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266956억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266914억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281830억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 281790억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297424억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 297386억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 312926억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 312890억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326497억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326464억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228865억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 228862억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238707억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238693억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245662억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245637억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254661억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254626억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266956억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266914억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281830억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 281790억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297424억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297386억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 312926억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 312890억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326497억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326464억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.435406753</v>
+        <v>0.435389649</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.335031363</v>
+        <v>0.334954499</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.134123237</v>
+        <v>0.134007441</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169299675</v>
+        <v>0.169138564</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.166433639</v>
+        <v>0.166264821</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.18065219</v>
+        <v>0.180551865</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210705716</v>
+        <v>0.210672249</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.228792108</v>
+        <v>0.228819699</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.223037605</v>
+        <v>0.2231032</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109962742</v>
+        <v>0.109964052</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109963551</v>
+        <v>0.109961024</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109963126</v>
+        <v>0.109962572</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109963349</v>
+        <v>0.109962754</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109964278</v>
+        <v>0.109964477</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109962001</v>
+        <v>0.10996267</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109962537</v>
+        <v>0.10996383</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.10996383</v>
+        <v>0.109963698</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109963359</v>
+        <v>0.10996355</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.007168551</v>
+        <v>0.006733918</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.006882867</v>
+        <v>0.00639959</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.00016423</v>
+        <v>-0.005402144</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.768259817</v>
+        <v>119.764996483</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.004908224</v>
+        <v>0.004003964</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.005815871</v>
+        <v>0.007192714</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>-0.006537124</v>
+        <v>0.002414405</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.775295367</v>
+        <v>119.764089538</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.005363792</v>
+        <v>0.003313123</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.01221158</v>
+        <v>0.010722536</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.007168551</v>
+        <v>0.006733918</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.006882867</v>
+        <v>0.00639959</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.00016423</v>
+        <v>-0.005402144</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.768259817</v>
+        <v>119.764996483</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004908224</v>
+        <v>0.004003964</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.005815871</v>
+        <v>0.007192714</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>-0.006537124</v>
+        <v>0.002414405</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.775295367</v>
+        <v>119.764089538</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.005363792</v>
+        <v>0.003313123</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.01221158</v>
+        <v>0.010722536</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7900,29 +7900,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213362478</v>
+        <v>0.213351325</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.088528598</v>
+        <v>0.088511029</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182297164</v>
+        <v>0.182268006</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178356413</v>
+        <v>0.178336762</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.138172209</v>
+        <v>0.138163238</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076599483</v>
+        <v>0.076589218</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132213869</v>
+        <v>0.132210147</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134331683</v>
+        <v>0.134330314</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8028,29 +8028,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.212867982</v>
+        <v>0.212845731</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.088354814</v>
+        <v>0.088338088</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.181959932</v>
+        <v>0.181949209</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.178085513</v>
+        <v>0.178064608</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.137994068</v>
+        <v>0.137984262</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.076512702</v>
+        <v>0.07649671500000001</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.132074726</v>
+        <v>0.132070997</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.134206805</v>
+        <v>0.134205426</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404320736607506</v>
+        <v>0.2404343313061502</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.06289894853106015</v>
+        <v>0.06289866939163283</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808335959910731</v>
+        <v>0.01808449705651839</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2680.3</v>
+        <v>2680.2</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>15190</v>
+        <v>14440</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>14050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>15040</v>
+        <v>14380</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15900</v>
+        <v>15656.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>15190</v>
+        <v>14440</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.67</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="32">
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228862억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 228853억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238693억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 238638억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245637억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 245535억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254626억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254476억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266914억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266725억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281790억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 281602억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297386억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 297203억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 312890억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 312715억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326464억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326300억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228862억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 228853억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238693억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238638억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245637억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245535억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254626억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254476억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266914억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266725억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281790억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 281602억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297386억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297203억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 312890억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 312715억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326464억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326300억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1986,19 +1986,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1879억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2046,19 +2046,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1879억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14440</v>
+        <v>14170</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>14050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>14380</v>
+        <v>13540</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15656.7</v>
+        <v>15445.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.435389649</v>
+        <v>0.435332633</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.334954499</v>
+        <v>0.334647042</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.134007441</v>
+        <v>0.133539806</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169138564</v>
+        <v>0.16844809</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.166264821</v>
+        <v>0.165484915</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180551865</v>
+        <v>0.180039694</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210672249</v>
+        <v>0.210425196</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.228819699</v>
+        <v>0.228860367</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.2231032</v>
+        <v>0.223356794</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109964052</v>
+        <v>0.109964448</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109961024</v>
+        <v>0.109964205</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109962572</v>
+        <v>0.109964718</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109962754</v>
+        <v>0.109964702</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109964477</v>
+        <v>0.109964043</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.10996267</v>
+        <v>0.10996441</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.10996383</v>
+        <v>0.109963483</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109963698</v>
+        <v>0.109964126</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.10996355</v>
+        <v>0.109962974</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.006733918</v>
+        <v>0.007261518</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.00639959</v>
+        <v>0.009513746</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.005402144</v>
+        <v>-0.002507817</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.764996483</v>
+        <v>119.772368813</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.004003964</v>
+        <v>0.01318002</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.007192714</v>
+        <v>0.002966883</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.002414405</v>
+        <v>0.008220086</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.764089538</v>
+        <v>119.764414446</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.003313123</v>
+        <v>0.008416641000000001</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.010722536</v>
+        <v>0.007980206</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.006733918</v>
+        <v>0.007261518</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.00639959</v>
+        <v>0.009513746</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.005402144</v>
+        <v>-0.002507817</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.764996483</v>
+        <v>119.772368813</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.004003964</v>
+        <v>0.01318002</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.007192714</v>
+        <v>0.002966883</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.002414405</v>
+        <v>0.008220086</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.764089538</v>
+        <v>119.764414446</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.003313123</v>
+        <v>0.008416641000000001</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.010722536</v>
+        <v>0.007980206</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7896,33 +7896,33 @@
         <v>0.36449665</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.310184103</v>
+        <v>0.310169492</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213351325</v>
+        <v>0.213309096</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.088511029</v>
+        <v>0.08843237299999999</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182268006</v>
+        <v>0.182188218</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178336762</v>
+        <v>0.178241303</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.138163238</v>
+        <v>0.138109154</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076589218</v>
+        <v>0.076528057</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132210147</v>
+        <v>0.132184989</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134330314</v>
+        <v>0.134313224</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8024,33 +8024,33 @@
         <v>0.362962457</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.309202668</v>
+        <v>0.309188103</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.212845731</v>
+        <v>0.212803596</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.088338088</v>
+        <v>0.08825957700000001</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.181949209</v>
+        <v>0.181861096</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.178064608</v>
+        <v>0.177977647</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.137984262</v>
+        <v>0.137930199</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.07649671500000001</v>
+        <v>0.076435595</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.132070997</v>
+        <v>0.132045813</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.134205426</v>
+        <v>0.134192669</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8713,11 +8713,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>14440</v>
+        <v>14170</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,660원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,210원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404343313061502</v>
+        <v>0.2404341343681027</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.06289866939163283</v>
+        <v>0.06289916970149008</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808449705651839</v>
+        <v>0.01808951736324206</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2680.2</v>
+        <v>2679.7</v>
       </c>
     </row>
     <row r="30">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.39</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="32">
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="33">
@@ -40385,7 +40385,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2762</v>
+        <v>0.2761</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228853억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 228852억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238638억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 238682억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245535억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 245625억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254476억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254609억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266725억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266902억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281602억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 281773억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297203억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 297366억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 312715억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 312870억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326300억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 326444억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228853억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 228852억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238638억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 238682억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245535억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245625억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254476억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254609억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266725억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266902억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281602억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 281773억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297203억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 297366억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 312715억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 312870억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326300억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 326444억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1986,19 +1986,19 @@
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1879억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2046,19 +2046,19 @@
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1879억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14170</v>
+        <v>14740</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15445.7</v>
+        <v>15366.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.435332633</v>
+        <v>0.435326932</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.334647042</v>
+        <v>0.334895372</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.133539806</v>
+        <v>0.133953997</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.16844809</v>
+        <v>0.169060311</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.165484915</v>
+        <v>0.166264141</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180039694</v>
+        <v>0.180537715</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210425196</v>
+        <v>0.210650757</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.228860367</v>
+        <v>0.22882714</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.223356794</v>
+        <v>0.223085831</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109964448</v>
+        <v>0.109964885</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109964205</v>
+        <v>0.109961465</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109964718</v>
+        <v>0.109963827</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109964702</v>
+        <v>0.109962239</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109964043</v>
+        <v>0.109962534</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.10996441</v>
+        <v>0.109961355</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109963483</v>
+        <v>0.109964476</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109964126</v>
+        <v>0.109963984</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109962974</v>
+        <v>0.109964411</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.007261518</v>
+        <v>0.007100742</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.009513746</v>
+        <v>0.009242396</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002507817</v>
+        <v>-0.002605496</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.772368813</v>
+        <v>119.767857463</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.01318002</v>
+        <v>-0.000755194</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.002966883</v>
+        <v>0.002413661</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.008220086</v>
+        <v>0.007593831</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.764414446</v>
+        <v>119.769319638</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.008416641000000001</v>
+        <v>-0.001467254</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.007980206</v>
+        <v>0.015972279</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.007261518</v>
+        <v>0.007100742</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.009513746</v>
+        <v>0.009242396</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002507817</v>
+        <v>-0.002605496</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.772368813</v>
+        <v>119.767857463</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.01318002</v>
+        <v>-0.000755194</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.002966883</v>
+        <v>0.002413661</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.008220086</v>
+        <v>0.007593831</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.764414446</v>
+        <v>119.769319638</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.008416641000000001</v>
+        <v>-0.001467254</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.007980206</v>
+        <v>0.015972279</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7900,29 +7900,29 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213309096</v>
+        <v>0.213342553</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.08843237299999999</v>
+        <v>0.088503465</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182188218</v>
+        <v>0.18226418</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178241303</v>
+        <v>0.178334714</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.138109154</v>
+        <v>0.138161364</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076528057</v>
+        <v>0.076581015</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132184989</v>
+        <v>0.132205486</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134313224</v>
+        <v>0.134327445</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8028,29 +8028,29 @@
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.212803596</v>
+        <v>0.212848099</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.08825957700000001</v>
+        <v>0.088329725</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.181861096</v>
+        <v>0.18192699</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.177977647</v>
+        <v>0.178063826</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.137930199</v>
+        <v>0.13798322</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.076435595</v>
+        <v>0.076494244</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.132045813</v>
+        <v>0.132066335</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.134192669</v>
+        <v>0.134202554</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8713,11 +8713,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>14170</v>
+        <v>14740</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 15,210원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,500원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404341343681027</v>
+        <v>0.2404330508805499</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.06289916970149008</v>
+        <v>0.06289855273246168</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808951736324206</v>
+        <v>0.01808510986290105</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2679.7</v>
+        <v>2680.1</v>
       </c>
     </row>
     <row r="30">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="32">
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33">
@@ -40385,7 +40385,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2761</v>
+        <v>0.2762</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 228852억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 229087억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 238682억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239056억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245625억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 245988억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254609억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 254846억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266902억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266692억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281773억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 281159억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 297366억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 296476억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 312870억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 311833억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 326444억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 325392억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 228852억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 229087억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 238682억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239056억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245625억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 245988억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254609억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 254846억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266902억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266692억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281773억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 281159억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 297366억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 296476억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 312870억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 311833억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 326444억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 325392억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1962,25 +1962,25 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1090억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1091억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1186억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1187억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1402억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1403억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1652억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1653억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1992,13 +1992,13 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2022,25 +2022,25 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1090억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1091억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1186억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1187억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1402억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1403억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1652억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1653억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2052,13 +2052,13 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2024억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2023억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2291억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14740</v>
+        <v>14710</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15366.2</v>
+        <v>15122.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.435326932</v>
+        <v>0.436803629</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.334895372</v>
+        <v>0.336982532</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.133953997</v>
+        <v>0.135628578</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.169060311</v>
+        <v>0.17015126</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.166264141</v>
+        <v>0.164148839</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.180537715</v>
+        <v>0.176125383</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.210650757</v>
+        <v>0.205245758</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.22882714</v>
+        <v>0.223609986</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.223085831</v>
+        <v>0.220105055</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109964885</v>
+        <v>0.109962977</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109961465</v>
+        <v>0.109962277</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109963827</v>
+        <v>0.109962469</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109962239</v>
+        <v>0.109961999</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109962534</v>
+        <v>0.109963902</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109961355</v>
+        <v>0.109964692</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.109964476</v>
+        <v>0.10996284</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109963984</v>
+        <v>0.109963382</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109964411</v>
+        <v>0.109962256</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.007100742</v>
+        <v>0.007062519</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.009242396</v>
+        <v>0.001896112</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>-0.002605496</v>
+        <v>0.004410178</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.767857463</v>
+        <v>119.761079046</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>-0.000755194</v>
+        <v>0.009613417000000001</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.002413661</v>
+        <v>0.006139878</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.007593831</v>
+        <v>0.002094103</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.769319638</v>
+        <v>119.765957942</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>-0.001467254</v>
+        <v>0.001402663</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>0.015972279</v>
+        <v>-0.000466204</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.007100742</v>
+        <v>0.007062519</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.009242396</v>
+        <v>0.001896112</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>-0.002605496</v>
+        <v>0.004410178</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.767857463</v>
+        <v>119.761079046</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>-0.000755194</v>
+        <v>0.009613417000000001</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.002413661</v>
+        <v>0.006139878</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.007593831</v>
+        <v>0.002094103</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.769319638</v>
+        <v>119.765957942</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>-0.001467254</v>
+        <v>0.001402663</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>0.015972279</v>
+        <v>-0.000466204</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7896,33 +7896,33 @@
         <v>0.36449665</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.310169492</v>
+        <v>0.31047633</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213342553</v>
+        <v>0.213627089</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.088503465</v>
+        <v>0.088755983</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.18226418</v>
+        <v>0.182305291</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178334714</v>
+        <v>0.178068016</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.138161364</v>
+        <v>0.137794202</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.076581015</v>
+        <v>0.07615675399999999</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.132205486</v>
+        <v>0.131807454</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.134327445</v>
+        <v>0.133978571</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8024,33 +8024,33 @@
         <v>0.362962457</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.309188103</v>
+        <v>0.30950855</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.212848099</v>
+        <v>0.213118583</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.088329725</v>
+        <v>0.08857266</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.18192699</v>
+        <v>0.181978218</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.178063826</v>
+        <v>0.177797731</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.13798322</v>
+        <v>0.137622672</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.076494244</v>
+        <v>0.076070076</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.132066335</v>
+        <v>0.1316631</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.134202554</v>
+        <v>0.133853935</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8713,11 +8713,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>14740</v>
+        <v>14710</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,100원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404330508805499</v>
+        <v>0.2404335986866963</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.06289855273246168</v>
+        <v>0.0628989001131673</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808510986290105</v>
+        <v>0.01808608882500858</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2680.1</v>
+        <v>2682.8</v>
       </c>
     </row>
     <row r="30">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.5</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="32">
@@ -40385,7 +40385,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2762</v>
+        <v>0.2764</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/033500_model.xlsx
+++ b/argus/kship/models/033500_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 229087억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 229261억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 239056억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 239366억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 245988억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 246321억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 254846억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 255116억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 266692억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 266658억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 281159억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 280815억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 296476억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 295920억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 311833억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 311165억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 325392억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
+고객지수 4분기 이동합(t−0) 324714억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -1590,55 +1590,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 229087억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 229261억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 239056억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 239366억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 245988억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 246321억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 254846억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 255116억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 266692억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 266658억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 281159억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 280815억 × 비례계수 0.0408 × 계절비중 Q1 0.232(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 296476억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 295920억 × 비례계수 0.0408 × 계절비중 Q2 0.254(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 311833억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 311165억 × 비례계수 0.0408 × 계절비중 Q3 0.244(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 325392억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
+        <t>추정: 고객지수 4분기 이동합(t−0) 324714억 × 비례계수 0.0408 × 계절비중 Q4 0.270(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.97, n=16, 창 19)
 [yoy]</t>
       </text>
     </comment>
@@ -1968,25 +1968,25 @@
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1187억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1188억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1403억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1404억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1653억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1654억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 1881억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -1998,7 +1998,7 @@
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 파생상품손익 0 + 기타금융손익 -0.46억(최근 4분기(2024Q4~2025Q3) 잔차 중위) (항등식); 이자손익 = 이자발생자산 2289억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2028,25 +2028,25 @@
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1187억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1188억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1403억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1404억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1653억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1654억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 1880억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 1881억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2058,7 +2058,7 @@
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 2290억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
+        <t>추정: 이자발생자산 2289억 × 1.81%(주석 이자수익 ÷ 평균 이자발생자산(2024Q4~2025Q3)) − 총차입금 0억 × 4.18%(주석 이자비용 ÷ 평균 총차입금(2024Q4~2025Q3)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4029,7 +4029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4900,35 +4900,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5019,35 +5019,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5138,35 +5138,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5257,35 +5257,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5376,35 +5376,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5495,35 +5495,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5614,35 +5614,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -5733,35 +5733,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -5868,7 +5868,7 @@
         <v>15900</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>14710</v>
+        <v>12980</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6050,7 +6050,7 @@
         <v>14050</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>13540</v>
+        <v>12250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6141,7 +6141,7 @@
         <v>16743.4</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>15122.7</v>
+        <v>14540.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -6296,33 +6296,33 @@
         <v>0.080234682</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.436803629</v>
+        <v>0.437892622</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.336982532</v>
+        <v>0.338720847</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.135628578</v>
+        <v>0.137169549</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.17015126</v>
+        <v>0.171384907</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.164148839</v>
+        <v>0.16311649</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.176125383</v>
+        <v>0.173162793</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>0.205245758</v>
+        <v>0.20135666</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>0.223609986</v>
+        <v>0.219704174</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>0.220105055</v>
+        <v>0.217719914</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -6607,39 +6607,39 @@
         <v>0.109964924</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.109962977</v>
+        <v>0.109962965</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.109962277</v>
+        <v>0.109965241</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.109962469</v>
+        <v>0.109962285</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.109961999</v>
+        <v>0.109964083</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.109963902</v>
+        <v>0.109964511</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.109964692</v>
+        <v>0.109963708</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.10996284</v>
+        <v>0.109963944</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.109963382</v>
+        <v>0.109964141</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.109962256</v>
+        <v>0.109962345</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -7509,36 +7509,36 @@
         <v/>
       </c>
       <c r="AC29" s="30" t="n">
-        <v>0.007062519</v>
+        <v>0.007215417</v>
       </c>
       <c r="AD29" s="30" t="n">
-        <v>0.001896112</v>
+        <v>0.001565521</v>
       </c>
       <c r="AE29" s="31" t="n"/>
       <c r="AF29" s="30" t="n">
-        <v>0.004410178</v>
+        <v>0.005715962</v>
       </c>
       <c r="AG29" s="30" t="n">
-        <v>119.761079046</v>
+        <v>119.771187898</v>
       </c>
       <c r="AH29" s="30" t="n">
-        <v>0.009613417000000001</v>
+        <v>-2.8529e-05</v>
       </c>
       <c r="AI29" s="30" t="n">
-        <v>0.006139878</v>
+        <v>0.009007312999999999</v>
       </c>
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="30" t="n">
-        <v>0.002094103</v>
+        <v>0.001762314</v>
       </c>
       <c r="AL29" s="30" t="n">
-        <v>119.765957942</v>
+        <v>119.7795889</v>
       </c>
       <c r="AM29" s="30" t="n">
-        <v>0.001402663</v>
+        <v>-0.002591378</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0.000466204</v>
+        <v>0.00529801</v>
       </c>
       <c r="AO29" s="31" t="n"/>
     </row>
@@ -7637,36 +7637,36 @@
         <v/>
       </c>
       <c r="AC30" s="30" t="n">
-        <v>0.007062519</v>
+        <v>0.007215417</v>
       </c>
       <c r="AD30" s="30" t="n">
-        <v>0.001896112</v>
+        <v>0.001565521</v>
       </c>
       <c r="AE30" s="31" t="n"/>
       <c r="AF30" s="30" t="n">
-        <v>0.004410178</v>
+        <v>0.005715962</v>
       </c>
       <c r="AG30" s="30" t="n">
-        <v>119.761079046</v>
+        <v>119.771187898</v>
       </c>
       <c r="AH30" s="30" t="n">
-        <v>0.009613417000000001</v>
+        <v>-2.8529e-05</v>
       </c>
       <c r="AI30" s="30" t="n">
-        <v>0.006139878</v>
+        <v>0.009007312999999999</v>
       </c>
       <c r="AJ30" s="31" t="n"/>
       <c r="AK30" s="30" t="n">
-        <v>0.002094103</v>
+        <v>0.001762314</v>
       </c>
       <c r="AL30" s="30" t="n">
-        <v>119.765957942</v>
+        <v>119.7795889</v>
       </c>
       <c r="AM30" s="30" t="n">
-        <v>0.001402663</v>
+        <v>-0.002591378</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0.000466204</v>
+        <v>0.00529801</v>
       </c>
       <c r="AO30" s="31" t="n"/>
     </row>
@@ -7896,33 +7896,33 @@
         <v>0.36449665</v>
       </c>
       <c r="AD32" s="24" t="n">
-        <v>0.31047633</v>
+        <v>0.310710111</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="24" t="n">
-        <v>0.213627089</v>
+        <v>0.213867677</v>
       </c>
       <c r="AG32" s="24" t="n">
-        <v>0.088755983</v>
+        <v>0.08897970400000001</v>
       </c>
       <c r="AH32" s="24" t="n">
-        <v>0.182305291</v>
+        <v>0.182393172</v>
       </c>
       <c r="AI32" s="24" t="n">
-        <v>0.178068016</v>
+        <v>0.177929775</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="24" t="n">
-        <v>0.137794202</v>
+        <v>0.137562517</v>
       </c>
       <c r="AL32" s="24" t="n">
-        <v>0.07615675399999999</v>
+        <v>0.075875725</v>
       </c>
       <c r="AM32" s="24" t="n">
-        <v>0.131807454</v>
+        <v>0.131520621</v>
       </c>
       <c r="AN32" s="24" t="n">
-        <v>0.133978571</v>
+        <v>0.133727133</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -8024,33 +8024,33 @@
         <v>0.362962457</v>
       </c>
       <c r="AD33" s="24" t="n">
-        <v>0.30950855</v>
+        <v>0.309741603</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="24" t="n">
-        <v>0.213118583</v>
+        <v>0.213347568</v>
       </c>
       <c r="AG33" s="24" t="n">
-        <v>0.08857266</v>
+        <v>0.08881515600000001</v>
       </c>
       <c r="AH33" s="24" t="n">
-        <v>0.181978218</v>
+        <v>0.182056182</v>
       </c>
       <c r="AI33" s="24" t="n">
-        <v>0.177797731</v>
+        <v>0.177666999</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="24" t="n">
-        <v>0.137622672</v>
+        <v>0.137378453</v>
       </c>
       <c r="AL33" s="24" t="n">
-        <v>0.076070076</v>
+        <v>0.07578979800000001</v>
       </c>
       <c r="AM33" s="24" t="n">
-        <v>0.1316631</v>
+        <v>0.131382172</v>
       </c>
       <c r="AN33" s="24" t="n">
-        <v>0.133853935</v>
+        <v>0.133607077</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -8713,11 +8713,11 @@
         </is>
       </c>
       <c r="D41" s="34" t="n">
-        <v>14710</v>
+        <v>12980</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 14,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 13,270원)</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D48" s="36" t="n">
-        <v>0.2404335986866963</v>
+        <v>0.2404326177348505</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="D49" s="36" t="n">
-        <v>0.0628989001131673</v>
+        <v>0.06289844352137816</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.01808608882500858</v>
+        <v>0.01808521874384756</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2682.8</v>
+        <v>2685.1</v>
       </c>
     </row>
     <row r="30">
@@ -40365,7 +40365,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.48</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="32">
@@ -40375,7 +40375,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="33">
@@ -40385,7 +40385,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2764</v>
+        <v>0.2767</v>
       </c>
     </row>
     <row r="34">
